--- a/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
+++ b/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Âm nhạc" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mĩ thuật" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Giáo dục thể chất" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoạt động trải nghiệm" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiếng Anh" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoạt động trải nghiệm" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -554,12 +555,12 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>1 – 3</t>
+          <t>1 – 2</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -589,12 +590,12 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>4 – 6</t>
+          <t>3 – 4</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -619,17 +620,17 @@
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Làm quen với các nét viết cơ bản, các chữ số, dấu thanh và bảng chữ cái</t>
+          <t>Làm quen với các nét cơ bản, các chữ số, bảng chữ cái và dấu thanh</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>6 tiết</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>7 – 9</t>
+          <t>5 – 10</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -659,12 +660,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>10 – 12</t>
+          <t>11 – 12</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -13668,7 +13669,7 @@
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: Âm thanh kì diệu — Học hát: Vào rừng hoa (Việt Anh)</t>
+          <t>Chủ đề 1: Âm thanh kì diệu — Thường thức âm nhạc: Âm thanh kì diệu; Học hát: Vào rừng hoa (Việt Anh)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -13702,7 +13703,7 @@
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: Âm thanh kì diệu — Ôn bài hát Vào rừng hoa; Thường thức âm nhạc: Câu chuyện "Âm thanh kì diệu"</t>
+          <t>Chủ đề 1: Âm thanh kì diệu — Ôn bài hát Vào rừng hoa; Đọc nhạc: Bậc thang Đô – Rê – Mi; Vận dụng – Sáng tạo: To – Nhỏ</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -13717,7 +13718,8 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1a: HS nghe các đoạn âm thanh GV mở từ học liệu số và nói được đó là tiếng gì.</t>
+          <t>Năng lực số 3.1 CB1a: HS cùng GV tạo bản ghi âm đoạn đọc to – nhỏ của lớp và nghe lại.
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -13770,7 +13772,7 @@
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: Âm thanh kì diệu — Vận dụng – Sáng tạo: To – Nhỏ</t>
+          <t>Chủ đề 1: Âm thanh kì diệu — Ôn bài hát Vào rừng hoa; Ôn đọc nhạc: Bậc thang Đô – Rê – Mi; Vận dụng – Sáng tạo: To – Nhỏ</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -13785,7 +13787,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1a: HS cùng GV tạo bản ghi âm đoạn đọc to – nhỏ của lớp và nghe lại.
+          <t>Năng lực số 1.1 CB1a: HS nhìn dòng nhạc Đô – Rê – Mi trên màn hình, nghe tiếng đàn và chỉ ra nốt được đọc to hơn.
 KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
@@ -13805,7 +13807,7 @@
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: Việt Nam yêu thương — Học hát: Tổ quốc ta (Mộng Lân)</t>
+          <t>Chủ đề 2: Việt Nam yêu thương — Học hát: Tổ quốc ta (Mộng Lân); Vận dụng – Sáng tạo: Cao – Thấp</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -13875,7 +13877,7 @@
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: Việt Nam yêu thương — Nhạc cụ: Gõ đệm trống con cho bài Tổ quốc ta; Nghe nhạc: Quốc ca (Văn Cao)</t>
+          <t>Chủ đề 2: Việt Nam yêu thương — Nghe nhạc: Quốc ca (Văn Cao); Nhạc cụ: Trống con</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -13910,7 +13912,7 @@
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: Việt Nam yêu thương — Vận dụng – Sáng tạo: Cao – Thấp</t>
+          <t>Chủ đề 2: Việt Nam yêu thương — Ôn bài hát Tổ quốc ta; Vận dụng – Sáng tạo: Cao – Thấp</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -13925,7 +13927,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1a: HS nghe âm thanh GV mở từ học liệu số và nói được âm nào cao, âm nào thấp.
+          <t>Năng lực số 1.1 CB1a: HS nghe tiếng kèn tu-ba, sáo pic-cô-lô GV mở từ học liệu số và nói được âm nào cao, âm nào thấp.
 QPAN: Chọn bài hát ca ngợi quê hương, đất nước, hoà bình; liên hệ hình ảnh chú bộ đội Quân đội nhân dân, chú công an Công an nhân dân và di tích lịch sử ở địa phương.</t>
         </is>
       </c>
@@ -13945,7 +13947,7 @@
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: Mái trường thân yêu — Học hát: Lớp Một thân yêu (Bùi Anh Tôn)</t>
+          <t>Chủ đề 3: Mái trường thân yêu — Học hát: Lớp Một thân yêu (Bùi Anh Tôn); Vận dụng – Sáng tạo: To – Nhỏ, Cao – Thấp</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -13960,7 +13962,8 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.3 CB1a: HS nói được tên bài hát Lớp Một thân yêu cùng tên tác giả Bùi Anh Tôn.</t>
+          <t>Năng lực số 3.3 CB1a: HS nói được tên bài hát Lớp Một thân yêu cùng tên tác giả Bùi Anh Tôn.
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -14047,7 +14050,7 @@
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: Mái trường thân yêu — Vận dụng – Sáng tạo: To – Nhỏ, Cao – Thấp</t>
+          <t>Chủ đề 3: Mái trường thân yêu — Ôn bài hát Lớp Một thân yêu; Ôn đọc nhạc: Ban nhạc Đô – Rê – Mi; Vận dụng – Sáng tạo: To – Nhỏ, Cao – Thấp</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -14252,7 +14255,7 @@
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Nhịp điệu mùa xuân — Học hát: Xúc xắc xúc xẻ (Nhạc: Nguyễn Ngọc Thiện, lời: phỏng theo đồng dao)</t>
+          <t>Chủ đề 5: Nhịp điệu mùa xuân — Học hát: Xúc xắc xúc xẻ (Nhạc: Nguyễn Ngọc Thiện, lời: phỏng theo đồng dao); Vận dụng – Sáng tạo: Dài – Ngắn</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -14267,7 +14270,8 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.3 CB1a: HS nói được tên bài hát cùng tên tác giả phần nhạc và nguồn lời ca phỏng theo đồng dao.</t>
+          <t>Năng lực số 3.3 CB1a: HS nói được tên bài hát cùng tên tác giả phần nhạc và nguồn lời ca phỏng theo đồng dao.
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14324,7 @@
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Nhịp điệu mùa xuân — Thường thức âm nhạc: Nhạc sĩ Mô-da (Câu chuyện "Thần đồng âm nhạc Mô-da"); Nghe nhạc: Khát vọng mùa xuân</t>
+          <t>Chủ đề 5: Nhịp điệu mùa xuân — Ôn đọc nhạc: Những người bạn của Đô – Rê – Mi; Thường thức âm nhạc: Nhạc sĩ Vôn-gang A-ma-đớt Mô-da (nghe bài hát Khát vọng mùa xuân); Vận dụng – Sáng tạo: Dài – Ngắn</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -14335,7 +14339,8 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1a: HS xem hình, nghe GV giới thiệu và nói được tên nhạc sĩ Mô-da, tên bản nhạc vừa nghe.</t>
+          <t>Năng lực số 1.1 CB1a: HS xem hình, nghe GV giới thiệu và nói được tên nhạc sĩ Mô-da, tên bài hát Khát vọng mùa xuân.
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14359,7 @@
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Nhịp điệu mùa xuân — Vận dụng – Sáng tạo: Dài – Ngắn</t>
+          <t>Chủ đề 5: Nhịp điệu mùa xuân — Ôn bài hát Xúc xắc xúc xẻ; Vận dụng – Sáng tạo: Dài – Ngắn</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -14389,7 +14394,7 @@
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Về miền dân ca — Học hát: Gà gáy (Dân ca Cống Khao, lời mới: Huy Trân)</t>
+          <t>Chủ đề 6: Về miền dân ca — Học hát: Gà gáy (Dân ca Cống Khao, lời mới: Huy Trân); Vận dụng – Sáng tạo: Dài – Ngắn</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -14404,7 +14409,8 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.3 CB1a: HS nói được bài Gà gáy là dân ca Cống Khao và người viết lời mới là Huy Trân.</t>
+          <t>Năng lực số 3.3 CB1a: HS nói được bài Gà gáy là dân ca Cống Khao và người viết lời mới là Huy Trân.
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -14423,7 +14429,7 @@
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Về miền dân ca — Ôn bài hát Gà gáy; Thường thức âm nhạc: "Câu chuyện về thanh phách"</t>
+          <t>Chủ đề 6: Về miền dân ca — Ôn bài hát Gà gáy; Nhạc cụ: Thanh phách</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -14438,7 +14444,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1a: HS xem hình, nghe âm thanh trên màn hình và nói đúng tên nhạc cụ thanh phách.</t>
+          <t>Năng lực số 3.1 CB1a: HS cùng GV ghi âm phần cả lớp hát Gà gáy kết hợp gõ thanh phách và nghe lại để nhận xét tiếng phách đã đều chưa.</t>
         </is>
       </c>
     </row>
@@ -14457,7 +14463,7 @@
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Về miền dân ca — Nhạc cụ: Thanh phách; Nghe nhạc: Lí cây bông (Dân ca Nam Bộ)</t>
+          <t>Chủ đề 6: Về miền dân ca — Thường thức âm nhạc: Câu chuyện về thanh phách; Vận dụng – Sáng tạo: Dài – Ngắn</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -14472,7 +14478,8 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 4.1 CB1a: HS ngồi đúng khoảng cách với màn hình, nghe loa vừa đủ khi xem, nghe bài Lí cây bông.</t>
+          <t>Năng lực số 1.1 CB1a: HS xem hình, nghe âm thanh trên màn hình và nói đúng tên nhạc cụ thanh phách.
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -14491,7 +14498,7 @@
       <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Về miền dân ca — Vận dụng – Sáng tạo: Dài – Ngắn</t>
+          <t>Chủ đề 6: Về miền dân ca — Ôn bài hát Gà gáy; Nghe nhạc: Lí cây bông (Dân ca Nam Bộ)</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -14506,8 +14513,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.1 CB1a: HS nói lời chào buổi sáng để GV ghi lại thành lời nhắn gửi bạn lớp bên.
-KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số 4.1 CB1a: HS ngồi đúng khoảng cách với màn hình, nghe loa vừa đủ khi xem, nghe bài Lí cây bông.</t>
         </is>
       </c>
     </row>
@@ -14526,7 +14532,7 @@
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: Gia đình — Học hát: Cây gia đình (Nhạc: Quỳnh Hợp, lời thơ: Nguyễn Thị Mai)</t>
+          <t>Chủ đề 7: Gia đình — Học hát: Cây gia đình (Nhạc: Quỳnh Hợp, lời thơ: Nguyễn Thị Mai); Vận dụng – Sáng tạo: Góc âm nhạc</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -14541,7 +14547,8 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.3 CB1a: HS nói được tên bài hát cùng tên tác giả nhạc và tác giả lời thơ.</t>
+          <t>Năng lực số 3.3 CB1a: HS nói được tên bài hát cùng tên tác giả nhạc và tác giả lời thơ.
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -14628,7 +14635,7 @@
       <c r="D32" s="4" t="inlineStr"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: Gia đình — Vận dụng – Sáng tạo: Góc âm nhạc</t>
+          <t>Chủ đề 7: Gia đình — Vận dụng – Sáng tạo: Góc âm nhạc; Ôn bài hát Cây gia đình</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -14697,7 +14704,7 @@
       <c r="D34" s="4" t="inlineStr"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: Vui đón hè — Ôn bài hát Ngôi sao lấp lánh; Nhạc cụ: Trai-en-gô</t>
+          <t>Chủ đề 8: Vui đón hè — Nhạc cụ: Trai-en-gô (triangle); Ôn bài hát Ngôi sao lấp lánh</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -18431,6 +18438,1363 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KẾ HOẠCH GIÁO DỤC MÔN TIẾNG ANH — LỚP 1 · NĂM HỌC 2026-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Cách dùng: giữ nguyên dòng tên cột và thứ tự cột · mỗi tiết một dòng · ô Tuần/Chủ đề/Tên bài để trống nghĩa là giống dòng trên · sửa xong lưu lại rồi vào Bút Xanh bấm "Nhập KHGD của tôi".</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Tuần</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Chủ đề/Mạch nội dung</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Tên bài</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Phân môn / Hoạt động</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Nội dung/Tên bài học</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Thời lượng</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Tiết KH</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Nội dung điều chỉnh, bổ sung</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Me and my friends</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Unit 1: In the school playground</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Unit 1: In the school playground – Lesson 1 (1, 2) &amp; Lesson 2 (3, 4, 5)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Guide pupils to access and open the lesson audio files on a safe digital learning resources website.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Me and my friends</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Unit 1: In the school playground</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Unit 1: In the school playground – Lesson 3</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Unit 2: In the dining room</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Unit 2: In the dining room – Lesson 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Unit 2: In the dining room</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Unit 2: In the dining room – Lesson 3</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 3.1.CB1a: Practise drawing a simple birthday cake in Paint
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 1</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3: At the street market</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3: At the street market – Lesson 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1b: Search safely for pictures of a country market
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Me and my friends</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3: At the street market</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3: At the street market – Lesson 3</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.C1.3: How an AI camera scans images and recognises circles and squares in real life.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom – Lesson 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom – Lesson 3</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop – Lesson 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.C1.1: Recognise the AI system in automatic ordering machines that quickly identifies fish dishes.
+Ethics: Know how to say "Thank you" when receiving food from parents or staff.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop – Lesson 3</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.D1.1: For a robot to know the types of milk, pupils need to show the machine pictures of strawberry milk and plain milk cartons so that it does not learn wrongly.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Unit 6: In the classroom</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Unit 6: In the classroom – Lesson 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.C1.1: Recognise AI in the smart interactive board that helps the teacher practise writing the letter Pp, pen, pencil.
+Digital competence 4.1.CB1a: Turn off the computer at the end of the lesson to protect the device.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Unit 6: In the classroom</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Unit 6: In the classroom – Lesson 3</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.A1.1: Discussion: Humans decide to use pencils to draw creative pictures; AI only follows commands.
+Digital competence 3.1.CB1a: Practise drawing a classroom object (a rectangle) on the computer.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 2</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.C1.1: Compare how fast pupils find words with how fast AI scans data to find the answer in an instant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Unit 7: In the garden</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Unit 7: In the garden – Lesson 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.C1.1: Recognise smart (AI) devices that automatically water the garden when the soil is dry.
+Ethics: Love nature and protect green trees.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Unit 7: In the garden</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Unit 7: In the garden – Lesson 3</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Unit 8: In the park</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Unit 8: In the park – Lesson 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Semester I Test &amp; Feedback – Self-check</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop – Lesson 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop – Lesson 3</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo – Lesson 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1b: Search the Internet for videos of monkey sounds under the teacher's safe guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo – Lesson 3</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.A1.1: Discussion: Humans decide what to feed animals; AI can only suggest menus based on available data.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 3</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Me and my friends</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop – Lesson 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 4.3.CB1a: Health risk warning: Do not walk while looking at a phone, so as to stay safe in the sun.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Me and my friends</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop – Lesson 3</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake – Lesson 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 3.1.CB1a: Practise drawing a simple digital leaf or lemon (lemons) on the computer.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake – Lesson 3</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen – Lesson 1, 2</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen – Lesson 3</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop – Lesson 1, 2</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 4.2.CB1b: Information security: Do not share photos of expensive gifts online, so that bad people cannot take advantage of them.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 4</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 3.3.CB1a: Respect copyright: Write your name on your drawing before submitting it to the teacher on the interactive board.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match – Lesson 1, 2</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match – Lesson 3</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home – Lesson 1, 2</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1b: Pupils sort pictures of houses into the "My Home" folder on the class computer.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Review 4: Self-check</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
+++ b/assets/docs/lop1/KHDH ca khoi - Lop 1.xlsx
@@ -5075,7 +5075,7 @@
       <c r="D135" s="4" t="inlineStr"/>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Bài 2: Lời chào</t>
+          <t>Bài 2: Lời chào đi trước</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -7078,7 +7078,8 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát hình động và đặt đúng dấu lớn hơn, bé hơn, bằng nhau giữa hai số.</t>
+          <t>Năng lực số 1.1 CB1b: HS quan sát hình động và đặt đúng dấu lớn hơn, bé hơn, bằng nhau giữa hai số.
+STEM: Dụng cụ so sánh số (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7109,8 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát hình động và đặt đúng dấu lớn hơn, bé hơn, bằng nhau giữa hai số.</t>
+          <t>Năng lực số 1.1 CB1b: HS quan sát hình động và đặt đúng dấu lớn hơn, bé hơn, bằng nhau giữa hai số.
+STEM: Dụng cụ so sánh số (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7320,8 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Thực hành cùng thẻ học Toán (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7351,8 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Thực hành cùng thẻ học Toán (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7452,8 @@
       <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Tích hợp AI - 1.C1.2: Hiểu camera là “mắt” giúp thiết bị/robot thu nhận hình ảnh; AI có thể xử lí hình ảnh để nhận diện các mảnh ghép khi thực hiện nhiệm vụ xếp hình.
-Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Thực hành trang trí lớp học bằng các hình hình học (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7484,8 @@
       <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Tích hợp AI - 1.C1.2: Hiểu camera là “mắt” giúp thiết bị/robot thu nhận hình ảnh; AI có thể xử lí hình ảnh để nhận diện các mảnh ghép khi thực hiện nhiệm vụ xếp hình.
-Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Thực hành trang trí lớp học bằng các hình hình học (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7962,8 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Dụng cụ tính cộng, tính trừ (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7997,8 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Dụng cụ tính cộng, tính trừ (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8028,8 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Thực hành tính nhẩm (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8059,8 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Thực hành tính nhẩm (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9374,8 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Mô hình tính hàng dọc (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -9394,7 +9405,8 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Mô hình tính hàng dọc (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -9490,6 +9502,7 @@
         <is>
           <t>Tích hợp AI 1.A2.1: Kể tên được một số thiết bị có sử dụng AI như loa thông minh, trợ lý ảo; biết dưới sự hướng dẫn của giáo viên có thể hỏi trợ lý ảo về thời gian để hỗ trợ xem giờ và quản lí lịch trình cá nhân.
 Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Đồng hồ tiện ích (Toán – Mĩ thuật) — dạy thay cho tiết này.
 KNS: KN quản lí thời gian: xem giờ, sắp xếp công việc trong ngày.</t>
         </is>
       </c>
@@ -9520,7 +9533,8 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Đồng hồ tiện ích (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10113,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CĐ 1: Tự chăm sóc</t>
+          <t>Chủ đề 1: Tự chăm sóc bản thân</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -10134,7 +10148,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CĐ 1: Tự chăm sóc</t>
+          <t>Chủ đề 1: Tự chăm sóc bản thân</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -10169,7 +10183,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CĐ 1: Tự chăm sóc</t>
+          <t>Chủ đề 1: Tự chăm sóc bản thân</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -10204,7 +10218,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CĐ 1: Tự chăm sóc</t>
+          <t>Chủ đề 1: Tự chăm sóc bản thân</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -10240,7 +10254,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CĐ 2: Yêu thương</t>
+          <t>Chủ đề 2: Yêu thương gia đình</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -10275,7 +10289,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CĐ 2: Yêu thương</t>
+          <t>Chủ đề 2: Yêu thương gia đình</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -16101,7 +16115,7 @@
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: Đội hình đội ngũ — Bài 1: Tư thế đứng nghiêm, đứng nghỉ (Tiết 1)</t>
+          <t>Chủ đề 1: Đội hình đội ngũ — Bài 1: Các tư thế đứng nghiêm, đứng nghỉ (Tiết 1)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -16136,7 +16150,7 @@
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: Đội hình đội ngũ — Bài 1: Tư thế đứng nghiêm, đứng nghỉ (Tiết 2)</t>
+          <t>Chủ đề 1: Đội hình đội ngũ — Bài 1: Các tư thế đứng nghiêm, đứng nghỉ (Tiết 2)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -16170,7 +16184,7 @@
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: Đội hình đội ngũ — Bài 1: Tư thế đứng nghiêm, đứng nghỉ (Tiết 3)</t>
+          <t>Chủ đề 1: Đội hình đội ngũ — Bài 1: Các tư thế đứng nghiêm, đứng nghỉ (Tiết 3)</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -18438,7 +18452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -18526,7 +18540,7 @@
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Unit 1: In the school playground – Lesson 1 (1, 2) &amp; Lesson 2 (3, 4, 5)</t>
+          <t>Unit 1: In the school playground – Lesson 1 (Activities 1–2)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -18540,70 +18554,71 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Listen to the word audio on the class computer and point to the right pictures on the projector (Bill, ball, bike and book).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Me and my friends</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Unit 1: In the school playground</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Unit 1: In the school playground – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Digital competence 1.3.CB1a: Guide pupils to access and open the lesson audio files on a safe digital learning resources website.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Me and my friends</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Unit 1: In the school playground</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Unit 1: In the school playground – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Me and my family</t>
+          <t>Me and my friends</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Unit 2: In the dining room</t>
+          <t>Unit 1: In the school playground</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Unit 2: In the dining room – Lesson 1 &amp; 2</t>
+          <t>Unit 1: In the school playground – Lesson 3 (Activities 6–8)</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -18618,14 +18633,15 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.1.CB1a: Listen to the lesson audio on the class computer and point to the right character on the screen to find the information they hear.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -18641,7 +18657,7 @@
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Unit 2: In the dining room – Lesson 3</t>
+          <t>Unit 2: In the dining room – Lesson 1 (Activities 1–2)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -18655,229 +18671,529 @@
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the pictures on the projector and listen to the audio on the class computer to find the right word (cake, car, cat, cup).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Unit 2: In the dining room</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Unit 2: In the dining room – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 2 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Unit 2: In the dining room</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Unit 2: In the dining room – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Digital competence 3.1.CB1a: Practise drawing a simple birthday cake in Paint
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 1 – Lesson 1</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the word pictures of Units 1 and 2 on the projector and find the right picture when they hear a word.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 1 – Lesson 2</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.2.CB1a: Look at the word pictures of Units 1 and 2 in a picture quiz on the projector and choose the right answer with the class.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Me and my family</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Fun time 1</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Me and the world around</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Unit 3: At the street market</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Unit 3: At the street market – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3: At the street market – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Digital competence 1.1.CB1b: Search safely for pictures of a country market
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Me and my friends</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Unit 3: At the street market</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Unit 3: At the street market – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3: At the street market – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 3 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3: At the street market</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3: At the street market – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>AI 1.C1.3: How an AI camera scans images and recognises circles and squares in real life.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Listen to the audio on the class computer and point to the right pictures in the Pupil’s Book (desk, dog, door, duck).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 4 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Unit 4: In the bedroom – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Watch and listen to the song on hoclieu.vn on the projector and follow the words and the actions.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Review 1 – Phil and Sue</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.2.CB1a: Look at the Phil and Sue story pictures on the projector and find simple information (who, what they see) to answer the teacher’s questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Review 1 – Self-check – Part 1</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Listen to the Self-check audio on the class computer and check their answers on the screen with the teacher’s guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Review 1 – Self-check – Part 2</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 5.2.CB1a: Choose a simple revision tool the teacher prepares (the audio, digital flashcards or a picture game) to practise the words.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Me and my family</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Unit 4: In the bedroom</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Unit 4: In the bedroom – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Me and my family</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Unit 4: In the bedroom</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Unit 4: In the bedroom – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Unit 5: At the fish and chip shop</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Unit 5: At the fish and chip shop – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>AI 1.C1.1: Recognise the AI system in automatic ordering machines that quickly identifies fish dishes.
 Ethics: Know how to say "Thank you" when receiving food from parents or staff.
@@ -18885,78 +19201,117 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Me and my school</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Unit 5: At the fish and chip shop</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Unit 5: At the fish and chip shop – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 5 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5: At the fish and chip shop – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>AI 1.D1.1: For a robot to know the types of milk, pupils need to show the machine pictures of strawberry milk and plain milk cartons so that it does not learn wrongly.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Me and my school</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Unit 6: In the classroom</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Unit 6: In the classroom – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Unit 6: In the classroom – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>AI 1.C1.1: Recognise AI in the smart interactive board that helps the teacher practise writing the letter Pp, pen, pencil.
 Digital competence 4.1.CB1a: Turn off the computer at the end of the lesson to protect the device.
@@ -18964,39 +19319,78 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Me and my school</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Unit 6: In the classroom</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Unit 6: In the classroom – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Unit 6: In the classroom – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 6 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Unit 6: In the classroom</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Unit 6: In the classroom – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>AI 1.A1.1: Discussion: Humans decide to use pencils to draw creative pictures; AI only follows commands.
 Digital competence 3.1.CB1a: Practise drawing a classroom object (a rectangle) on the computer.
@@ -19004,69 +19398,109 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Fun time 2</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>AI 1.C1.1: Compare how fast pupils find words with how fast AI scans data to find the answer in an instant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 2 – Lesson 1</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.C1.1: Compare how fast pupils find words with how fast AI scans data to find the answer in an instant.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 2 – Lesson 2</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.2.CB1a: Look at the word pictures of Units 5 and 6 in a picture quiz on the projector and choose the right answer with the class.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Me and my family</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Unit 7: In the garden</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Unit 7: In the garden – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Unit 7: In the garden – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>AI 1.C1.1: Recognise smart (AI) devices that automatically water the garden when the soil is dry.
 Ethics: Love nature and protect green trees.
@@ -19074,416 +19508,26 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Me and my family</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Unit 7: In the garden</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Unit 7: In the garden – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Me and my family</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Unit 8: In the park</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Unit 8: In the park – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr"/>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Semester I Test &amp; Feedback – Self-check</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Me and the world around</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Unit 9: In the shop</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Unit 9: In the shop – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Me and the world around</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Unit 9: In the shop</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Unit 9: In the shop – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Me and the world around</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10: At the zoo</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10: At the zoo – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence 1.1.CB1b: Search the Internet for videos of monkey sounds under the teacher's safe guidance.
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Me and the world around</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10: At the zoo</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10: At the zoo – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>AI 1.A1.1: Discussion: Humans decide what to feed animals; AI can only suggest menus based on available data.
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr"/>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Fun time 3</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Me and my friends</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11: At the bus stop</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11: At the bus stop – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence 4.3.CB1a: Health risk warning: Do not walk while looking at a phone, so as to stay safe in the sun.
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Me and my friends</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11: At the bus stop</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11: At the bus stop – Lesson 3</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr"/>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Unit 12: At the lake</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Unit 12: At the lake – Lesson 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence 3.1.CB1a: Practise drawing a simple digital leaf or lemon (lemons) on the computer.
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Unit 12: At the lake</t>
+          <t>Unit 7: In the garden</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Unit 12: At the lake – Lesson 3</t>
+          <t>Unit 7: In the garden – Lesson 2 (Activities 3–5)</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -19498,30 +19542,31 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 7 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Me and my school</t>
+          <t>Me and my family</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Unit 13: In the school canteen</t>
+          <t>Unit 7: In the garden</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Unit 13: In the school canteen – Lesson 1, 2</t>
+          <t>Unit 7: In the garden – Lesson 3 (Activities 6–8)</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -19536,30 +19581,31 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.1.CB1a: Look at the poster on the projector and listen to the song audio to find the girl, the goat and the gate.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Me and my school</t>
+          <t>Me and my family</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Unit 13: In the school canteen</t>
+          <t>Unit 8: In the park</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Unit 13: In the school canteen – Lesson 3</t>
+          <t>Unit 8: In the park – Lesson 1 (Activities 1–2)</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -19574,30 +19620,31 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.1.CB1a: Listen to the audio on the class computer and point to the right body part or picture (hair, hand, head, horse).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Me and my school</t>
+          <t>Me and my family</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Unit 14: In the toy shop</t>
+          <t>Unit 8: In the park</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Unit 14: In the toy shop – Lesson 1, 2</t>
+          <t>Unit 8: In the park – Lesson 2 (Activities 3–5)</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -19612,7 +19659,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Digital competence 4.2.CB1b: Information security: Do not share photos of expensive gifts online, so that bad people cannot take advantage of them.
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 8 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -19620,15 +19667,23 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr"/>
-      <c r="C34" s="4" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Unit 8: In the park</t>
+        </is>
+      </c>
       <c r="D34" s="4" t="inlineStr"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Fun time 4</t>
+          <t>Unit 8: In the park – Lesson 3 (Activities 6–8)</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -19643,26 +19698,27 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Digital competence 3.3.CB1a: Respect copyright: Write your name on your drawing before submitting it to the teacher on the interactive board.</t>
+          <t>Digital competence 1.1.CB1a: Listen to the song audio on the class computer and touch the right body part (hair, hand, head).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr"/>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Unit 15: At the football match</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Unit 15: At the football match – Lesson 1, 2</t>
+          <t>Review 2 – Phil and Sue</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -19677,30 +19733,26 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.2.CB1a: Look at the Phil and Sue story pictures on the projector and find simple information (who, what they see) to answer the teacher’s questions.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Me and my school</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Unit 15: At the football match</t>
-        </is>
-      </c>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
       <c r="D36" s="4" t="inlineStr"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Unit 15: At the football match – Lesson 3</t>
+          <t>Review 2 – Self-check – Part 1</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -19715,26 +19767,26 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 1.1.CB1a: Listen to the Self-check audio on the class computer and check their answers on the screen with the teacher’s guidance.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr"/>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Unit 16: At home</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
       <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Unit 16: At home – Lesson 1, 2</t>
+          <t>Review 2 – Self-check – Part 2</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -19749,23 +19801,26 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Digital competence 1.3.CB1b: Pupils sort pictures of houses into the "My Home" folder on the class computer.
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Digital competence 5.2.CB1a: Choose a simple revision tool the teacher prepares (the audio, digital flashcards or a picture game) to practise the words.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Reserve / Consolidation</t>
+        </is>
+      </c>
       <c r="C38" s="4" t="inlineStr"/>
       <c r="D38" s="4" t="inlineStr"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Review 4: Self-check</t>
+          <t>Reserve period 1</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -19778,7 +19833,1325 @@
           <t>35</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 2.4.CB1a: Take part in a simple picture quiz on the projector, taking turns and cheering politely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the flashcard pictures on the projector and listen to the audio to find the right things in the shop (clocks, locks, mops, pots).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 9 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Unit 9: In the shop – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Count the things in the pictures on the projector and listen to the audio to check their answers.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1b: Search the Internet for videos of monkey sounds under the teacher's safe guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 10 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10: At the zoo – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>AI 1.A1.1: Discussion: Humans decide what to feed animals; AI can only suggest menus based on available data.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 3 – Lesson 1</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the pictures of Units 9 and 10 on the projector and find the right picture when they hear a word.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 3 – Lesson 2</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.2.CB1a: Look at the word pictures of Units 9 and 10 in a picture quiz on the projector and choose the right answer with the class.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Me and my friends</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 4.3.CB1a: Know the health risk of walking while looking at a phone, and stay safe in the sun.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Me and my friends</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 11 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Me and my friends</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11: At the bus stop – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the pictures on the projector and listen to the audio to find who is running (he or she).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 3.1.CB1a: Practise drawing a simple digital leaf or lemon (lemons) on the computer.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 12 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Me and the world around</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12: At the lake – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the pictures on the projector and listen to the song audio to find Lucy, the lake, the leaf and the lemons.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Review 3 – Phil and Sue</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.2.CB1a: Look at the Phil and Sue story pictures on the projector and find simple information (who, what they see) to answer the teacher’s questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Review 3 – Self-check – Part 1</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Listen to the Self-check audio on the class computer and check their answers on the screen with the teacher’s guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Review 3 – Self-check – Part 2</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 5.2.CB1a: Choose a simple revision tool the teacher prepares (the audio, digital flashcards or a picture game) to practise the words.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Listen to the audio on the class computer and point to the right food pictures (bananas, noodles, nuts).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 13 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13: In the school canteen – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the canteen pictures on the projector and listen to the audio to find what he or she is having.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 4.2.CB1b: Information security: Do not share photos of expensive gifts online, so that bad people cannot take advantage of them.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 14 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14: In the toy shop – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Look at the toy shop picture on the projector and listen to the audio to find the toys they hear.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 4 – Lesson 1</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 3.3.CB1a: Respect copyright: Write your name on your drawing before submitting it to the teacher on the interactive board.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Fun time</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Fun time 4 – Lesson 2</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.2.CB1a: Look at the word pictures of Units 13 and 14 in a picture quiz on the projector and choose the right answer with the class.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Listen to the audio on the class computer and point to the right pictures (face, father, foot, football).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 15 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Me and my school</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15: At the football match – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Watch the song pictures on the projector, listen and point to the right body parts.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home – Lesson 1 (Activities 1–2)</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1b: Pupils sort pictures of houses into the "My Home" folder on the class computer.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home – Lesson 2 (Activities 3–5)</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.3.CB1a: Watch and listen to the Unit 16 chant on the safe learning website hoclieu.vn on the projector with the teacher’s guidance.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Me and my family</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Unit 16: At home – Lesson 3 (Activities 6–8)</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Count the things in the picture on the projector and listen to the audio to check the numbers (six to ten).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Review 4 – Phil and Sue</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.2.CB1a: Look at the Phil and Sue story pictures on the projector and find simple information (who, what they see) to answer the teacher’s questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr"/>
+      <c r="D71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Review 4 – Self-check – Part 1</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 1.1.CB1a: Listen to the Self-check audio on the class computer and check their answers on the screen with the teacher’s guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Revision / Self-check</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Review 4 – Self-check – Part 2</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 5.2.CB1a: Choose a simple revision tool the teacher prepares (the audio, digital flashcards or a picture game) to practise the words.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Reserve / Consolidation</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr"/>
+      <c r="D73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Reserve period 2</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence 2.4.CB1a: Take part in a simple picture quiz on the projector, taking turns and cheering politely.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -20730,7 +22103,7 @@
       <c r="H29" s="4" t="inlineStr">
         <is>
           <t>Năng lực số 2.5 CB1a: HS xem phim tình huống và chọn được cách ứng xử phù hợp với bạn bè, thầy cô.
-QPAN: Tổ chức hoạt động tìm hiểu, thăm hỏi, tri ân gia đình thương binh, liệt sĩ, đơn vị bộ đội, công an trên địa bàn; giới thiệu hình ảnh chú bộ đội Quân đội nhân dân, chú công an Công an nhân dân và di tích lịch sử ở địa phương.</t>
+Học tập và làm theo Bác: Điều 3 “Đoàn kết tốt, kỉ luật tốt” (mạch 3): HS nói một việc thân thiện đã làm cho bạn hôm nay (chào bạn, cho bạn mượn bút, rủ bạn chơi cùng); GV chốt: đó là làm theo lời Bác dạy “đoàn kết tốt”.</t>
         </is>
       </c>
     </row>
@@ -20798,7 +22171,8 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Học tập và làm theo Bác: Năm điều Bác Hồ dạy (mạch 1–5): HS cả trường đọc đồng thanh Năm điều; mỗi lớp chọn một điều làm nội dung thi đua của lớp trong tháng và nói một việc cụ thể sẽ làm.
+KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
         </is>
       </c>
     </row>
@@ -20832,7 +22206,8 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.5 CB1a: HS xem phim tình huống và chọn được cách ứng xử phù hợp với bạn bè, thầy cô.</t>
+          <t>Năng lực số 2.5 CB1a: HS xem phim tình huống và chọn được cách ứng xử phù hợp với bạn bè, thầy cô.
+Học tập và làm theo Bác: Năm điều Bác Hồ dạy (mạch 1–5): mỗi HS nhận một việc nhỏ theo một điều (VD điều 4: rửa tay trước khi ăn, giữ bàn học sạch), làm trong tuần và kể lại ở giờ sinh hoạt Sao cuối tuần.</t>
         </is>
       </c>
     </row>
@@ -22671,7 +24046,7 @@
       <c r="D88" s="4" t="inlineStr"/>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Sinh hoạt dướ cờ: Chăm sóc vườn cây nhà trường</t>
+          <t>Sinh hoạt dưới cờ: Chăm sóc vườn cây nhà trường</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
